--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/8908-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/8908-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1050C5D2-4A1D-4A7A-A897-28E86C8B5153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{02C8BC94-F3EB-4018-920E-863A995F1E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{477FFDFB-26C8-4B56-97AE-B47F1E2F3A46}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{B3B7BA82-50FA-4CFF-859B-11ADB2CE5058}"/>
   </bookViews>
   <sheets>
     <sheet name="8908-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1586,29 +1586,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{564FF3BC-4F0E-40F0-B34E-5FBDA70CB366}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E69EEA5-9862-41C2-9397-B4BE7D389678}">
   <dimension ref="A1:X47"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1642,7 +1641,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1678,7 +1677,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1730,7 +1729,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1798,7 +1797,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1870,7 +1869,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39"/>
       <c r="B6" s="40"/>
       <c r="C6" s="13" t="s">
@@ -1898,7 +1897,7 @@
       <c r="W6" s="46"/>
       <c r="X6" s="42"/>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="47">
         <v>2023</v>
       </c>
@@ -1970,7 +1969,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="49"/>
       <c r="B8" s="50"/>
       <c r="C8" s="16" t="s">
@@ -1998,7 +1997,7 @@
       <c r="W8" s="56"/>
       <c r="X8" s="52"/>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2022</v>
       </c>
@@ -2070,7 +2069,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39"/>
       <c r="B10" s="40"/>
       <c r="C10" s="13" t="s">
@@ -2098,7 +2097,7 @@
       <c r="W10" s="46"/>
       <c r="X10" s="42"/>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="47">
         <v>2021</v>
       </c>
@@ -2170,7 +2169,7 @@
         <v>3.34</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="49"/>
       <c r="B12" s="50"/>
       <c r="C12" s="16" t="s">
@@ -2198,7 +2197,7 @@
       <c r="W12" s="56"/>
       <c r="X12" s="52"/>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2020</v>
       </c>
@@ -2270,7 +2269,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39"/>
       <c r="B14" s="40"/>
       <c r="C14" s="13" t="s">
@@ -2298,7 +2297,7 @@
       <c r="W14" s="46"/>
       <c r="X14" s="42"/>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="47">
         <v>2019</v>
       </c>
@@ -2370,7 +2369,7 @@
         <v>5.0599999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="49"/>
       <c r="B16" s="50"/>
       <c r="C16" s="16" t="s">
@@ -2398,7 +2397,7 @@
       <c r="W16" s="56"/>
       <c r="X16" s="52"/>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2018</v>
       </c>
@@ -2470,7 +2469,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39"/>
       <c r="B18" s="40"/>
       <c r="C18" s="13" t="s">
@@ -2498,7 +2497,7 @@
       <c r="W18" s="46"/>
       <c r="X18" s="42"/>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="47">
         <v>2017</v>
       </c>
@@ -2570,7 +2569,7 @@
         <v>5.07</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="49"/>
       <c r="B20" s="50"/>
       <c r="C20" s="16" t="s">
@@ -2598,7 +2597,7 @@
       <c r="W20" s="56"/>
       <c r="X20" s="52"/>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="57">
         <v>2016</v>
       </c>
@@ -2670,7 +2669,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="59">
         <v>2015</v>
       </c>
@@ -2742,7 +2741,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="57">
         <v>2014</v>
       </c>
@@ -2814,7 +2813,7 @@
         <v>5.39</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="59">
         <v>2013</v>
       </c>
@@ -2886,7 +2885,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="57">
         <v>2012</v>
       </c>
@@ -2958,7 +2957,7 @@
         <v>6.51</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="59">
         <v>2011</v>
       </c>
@@ -3030,7 +3029,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="57">
         <v>2010</v>
       </c>
@@ -3102,7 +3101,7 @@
         <v>7.84</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="59">
         <v>2009</v>
       </c>
@@ -3174,7 +3173,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="57">
         <v>2008</v>
       </c>
@@ -3246,7 +3245,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="59">
         <v>2007</v>
       </c>
@@ -3318,7 +3317,7 @@
         <v>5.94</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="57">
         <v>2006</v>
       </c>
@@ -3390,7 +3389,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="59">
         <v>2005</v>
       </c>
@@ -3462,7 +3461,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="57">
         <v>2004</v>
       </c>
@@ -3534,7 +3533,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="59">
         <v>2003</v>
       </c>
@@ -3606,7 +3605,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="57">
         <v>2002</v>
       </c>
@@ -3678,7 +3677,7 @@
         <v>3.65</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="59">
         <v>2001</v>
       </c>
@@ -3750,7 +3749,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="57">
         <v>2000</v>
       </c>
@@ -3822,7 +3821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="59">
         <v>1999</v>
       </c>
@@ -3894,7 +3893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="57">
         <v>1998</v>
       </c>
@@ -3966,7 +3965,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="59">
         <v>1997</v>
       </c>
@@ -4038,7 +4037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="57">
         <v>1996</v>
       </c>
@@ -4110,7 +4109,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="47">
         <v>1995</v>
       </c>
@@ -4182,7 +4181,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="49"/>
       <c r="B43" s="50"/>
       <c r="C43" s="16" t="s">
@@ -4210,7 +4209,7 @@
       <c r="W43" s="56"/>
       <c r="X43" s="52"/>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="57">
         <v>1994</v>
       </c>
@@ -4282,7 +4281,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="59">
         <v>1993</v>
       </c>
@@ -4354,7 +4353,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="57">
         <v>1992</v>
       </c>
@@ -4426,7 +4425,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="59" t="s">
         <v>64</v>
       </c>
